--- a/artfynd/A 46969-2024 artfynd.xlsx
+++ b/artfynd/A 46969-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Carl Jansson, Irena Koelemeijer, Maja Östlund, Noel Wieser</t>
+          <t>Noel Wieser, Maja Östlund, Irena Koelemeijer, Carl Jansson, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 46969-2024 artfynd.xlsx
+++ b/artfynd/A 46969-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136300004</v>
       </c>
       <c r="B2" t="n">
-        <v>92098</v>
+        <v>92101</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Noel Wieser, Maja Östlund, Irena Koelemeijer, Carl Jansson, Isak Vahlström</t>
+          <t>Isak Vahlström, Carl Jansson, Irena Koelemeijer, Maja Östlund, Noel Wieser</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 46969-2024 artfynd.xlsx
+++ b/artfynd/A 46969-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136300004</v>
       </c>
       <c r="B2" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Carl Jansson, Irena Koelemeijer, Maja Östlund, Noel Wieser</t>
+          <t>Noel Wieser, Maja Östlund, Irena Koelemeijer, Carl Jansson, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 46969-2024 artfynd.xlsx
+++ b/artfynd/A 46969-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136300004</v>
       </c>
       <c r="B2" t="n">
-        <v>92102</v>
+        <v>92107</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 46969-2024 artfynd.xlsx
+++ b/artfynd/A 46969-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136300004</v>
       </c>
       <c r="B2" t="n">
-        <v>92107</v>
+        <v>92109</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Noel Wieser, Maja Östlund, Irena Koelemeijer, Carl Jansson, Isak Vahlström</t>
+          <t>Isak Vahlström, Carl Jansson, Irena Koelemeijer, Maja Östlund, Noel Wieser</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
